--- a/config/brands.xlsx
+++ b/config/brands.xlsx
@@ -859,7 +859,7 @@
       </c>
       <c r="J2" s="6" t="inlineStr">
         <is>
-          <t>G11. Luxury cosmetics/skincare. Dept store. ADDED — was missing</t>
+          <t>Luxury cosmetics/skincare. Dept store. ADDED — was missing</t>
         </is>
       </c>
     </row>
@@ -905,7 +905,7 @@
       </c>
       <c r="J3" s="6" t="inlineStr">
         <is>
-          <t>G11. Prestige makeup. Strengthened base lineup. ADDED</t>
+          <t>Prestige makeup. Strengthened base lineup. ADDED</t>
         </is>
       </c>
     </row>
@@ -951,7 +951,7 @@
       </c>
       <c r="J4" s="8" t="inlineStr">
         <is>
-          <t>G11. Prestige skincare. Europe-focused, lower JP relevance. ADDED</t>
+          <t>Prestige skincare. Europe-focused, lower JP relevance. ADDED</t>
         </is>
       </c>
     </row>
@@ -997,7 +997,7 @@
       </c>
       <c r="J5" s="10" t="inlineStr">
         <is>
-          <t>G11. Rebranded 2019. UV serum + cream foundation hits. EXISTING — reclassified. DEDUP NOTE: カネボウ overlaps with sub-brands (KATE 21, LUNASOL 20, ALLIE 37, suisai 12, Evita 14, Primavista 1 = 105 overlaps). 227 Kanebo-only products. Use NOT LIKE exclusions at query time.</t>
+          <t>Rebranded 2019. UV serum + cream foundation hits. EXISTING — reclassified. DEDUP NOTE: カネボウ overlaps with sub-brands (KATE 21, LUNASOL 20, ALLIE 37, suisai 12, Evita 14, Primavista 1 = 105 overlaps). 227 Kanebo-only products. Use NOT LIKE exclusions at query time.</t>
         </is>
       </c>
     </row>
@@ -1043,7 +1043,7 @@
       </c>
       <c r="J6" s="10" t="inlineStr">
         <is>
-          <t>G11. Prestige skincare under Sofina. "est the lotion" is hero product. ADDED. KEYWORD FIXED 2026-03-31: エスト 化粧品 returns 0 hits; est公式 returns 7 clean products.</t>
+          <t>Prestige skincare under Sofina. "est the lotion" is hero product. ADDED. KEYWORD FIXED 2026-03-31: エスト 化粧品 returns 0 hits; est公式 returns 7 clean products.</t>
         </is>
       </c>
     </row>
@@ -1089,7 +1089,7 @@
       </c>
       <c r="J7" s="10" t="inlineStr">
         <is>
-          <t>G11. Prestige skincare. Renamed from Sofina. EXISTING — corrected</t>
+          <t>Prestige skincare. Renamed from Sofina. EXISTING — corrected</t>
         </is>
       </c>
     </row>
@@ -1135,7 +1135,7 @@
       </c>
       <c r="J8" s="12" t="inlineStr">
         <is>
-          <t>G11. Mass cosmetics. Lip Monster = #1 lipstick in Japan since 2021. EXISTING</t>
+          <t>Mass cosmetics. Lip Monster = #1 lipstick in Japan since 2021. EXISTING</t>
         </is>
       </c>
     </row>
@@ -1181,7 +1181,7 @@
       </c>
       <c r="J9" s="14" t="inlineStr">
         <is>
-          <t>G11. Sensitive skin. DIRECTLY relevant to "honest skincare" hypothesis. ADDED. LOW RAKUTEN COVERAGE: only 1 genuine product found. Flag low-confidence in NB05a.</t>
+          <t>Sensitive skin. DIRECTLY relevant to "honest skincare" hypothesis. ADDED. LOW RAKUTEN COVERAGE: only 1 genuine product found.</t>
         </is>
       </c>
     </row>
@@ -1229,7 +1229,7 @@
       </c>
       <c r="J10" s="14" t="inlineStr">
         <is>
-          <t>G11. Dry/sensitive skin. Ceramide-based. @cosme brand ID 264. EXISTING</t>
+          <t>Dry/sensitive skin. Ceramide-based. @cosme brand ID 264. EXISTING</t>
         </is>
       </c>
     </row>
@@ -1275,7 +1275,7 @@
       </c>
       <c r="J11" s="6" t="inlineStr">
         <is>
-          <t>R8. #1 prestige eyeshadow in Japan. Strong inbound demand. ADDED</t>
+          <t>#1 prestige eyeshadow in Japan. Strong inbound demand. ADDED</t>
         </is>
       </c>
     </row>
@@ -1321,7 +1321,7 @@
       </c>
       <c r="J12" s="16" t="inlineStr">
         <is>
-          <t>R8. Sun protection. Chrono Beauty line. Competes with Anessa. ADDED</t>
+          <t>Sun protection. Chrono Beauty line. Competes with Anessa. ADDED</t>
         </is>
       </c>
     </row>
@@ -1367,7 +1367,7 @@
       </c>
       <c r="J13" s="18" t="inlineStr">
         <is>
-          <t>R8. Base makeup under Sofina. Sweat-proof foundation. ADDED</t>
+          <t>Base makeup under Sofina. Sweat-proof foundation. ADDED</t>
         </is>
       </c>
     </row>
@@ -1459,7 +1459,7 @@
       </c>
       <c r="J15" s="22" t="inlineStr">
         <is>
-          <t>R8. Kanebo skincare. Replaced by other brands in focus. ADDED</t>
+          <t>Kanebo skincare. Replaced by other brands in focus. ADDED</t>
         </is>
       </c>
     </row>
@@ -1505,7 +1505,7 @@
       </c>
       <c r="J16" s="22" t="inlineStr">
         <is>
-          <t>R8. Anti-aging. Lower priority. ADDED</t>
+          <t>Anti-aging. Lower priority. ADDED</t>
         </is>
       </c>
     </row>
@@ -3231,7 +3231,7 @@
       </c>
       <c r="D2" s="33" t="inlineStr">
         <is>
-          <t>Primary target. Curél, freeplus, Bioré, KATE, Kanebo, Sofina iP, suisai, ALLIE, Primavista, LUNASOL, RMK, SUQQU</t>
+          <t>Curél, freeplus, Bioré, KATE, Kanebo, Sofina iP, suisai, ALLIE, Primavista, LUNASOL, RMK, SUQQU</t>
         </is>
       </c>
     </row>
@@ -3450,7 +3450,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="50" t="inlineStr">
         <is>
-          <t>ADDED (Kao)</t>
+          <t>ADDED</t>
         </is>
       </c>
       <c r="B2" s="51" t="inlineStr">
@@ -3467,7 +3467,7 @@
     <row r="3" ht="16" customHeight="1">
       <c r="A3" s="50" t="inlineStr">
         <is>
-          <t>ADDED (Kao)</t>
+          <t>ADDED</t>
         </is>
       </c>
       <c r="B3" s="51" t="inlineStr">
@@ -3484,7 +3484,7 @@
     <row r="4" ht="16" customHeight="1">
       <c r="A4" s="50" t="inlineStr">
         <is>
-          <t>ADDED (Kao)</t>
+          <t>ADDED</t>
         </is>
       </c>
       <c r="B4" s="51" t="inlineStr">
@@ -3494,14 +3494,14 @@
       </c>
       <c r="C4" s="51" t="inlineStr">
         <is>
-          <t>Prestige skincare. G11. Europe-focused, set as non-target.</t>
+          <t>Prestige skincare. Europe-focused, set as non-target.</t>
         </is>
       </c>
     </row>
     <row r="5" ht="16" customHeight="1">
       <c r="A5" s="50" t="inlineStr">
         <is>
-          <t>ADDED (Kao)</t>
+          <t>ADDED</t>
         </is>
       </c>
       <c r="B5" s="51" t="inlineStr">
@@ -3511,14 +3511,14 @@
       </c>
       <c r="C5" s="51" t="inlineStr">
         <is>
-          <t>Prestige skincare under Sofina. G11. "est the lotion" hero product.</t>
+          <t>Prestige skincare under Sofina. "est the lotion" hero product.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="16" customHeight="1">
       <c r="A6" s="50" t="inlineStr">
         <is>
-          <t>ADDED (Kao)</t>
+          <t>ADDED</t>
         </is>
       </c>
       <c r="B6" s="51" t="inlineStr">
@@ -3535,7 +3535,7 @@
     <row r="7" ht="16" customHeight="1">
       <c r="A7" s="50" t="inlineStr">
         <is>
-          <t>ADDED (Kao)</t>
+          <t>ADDED</t>
         </is>
       </c>
       <c r="B7" s="51" t="inlineStr">
@@ -3545,14 +3545,14 @@
       </c>
       <c r="C7" s="51" t="inlineStr">
         <is>
-          <t>Sensitive skin brand. G11. DIRECTLY supports "honest skincare" hypothesis.</t>
+          <t>Sensitive skin brand. DIRECTLY supports "honest skincare" hypothesis.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="16" customHeight="1">
       <c r="A8" s="50" t="inlineStr">
         <is>
-          <t>ADDED (Kao)</t>
+          <t>ADDED</t>
         </is>
       </c>
       <c r="B8" s="51" t="inlineStr">
@@ -3562,14 +3562,14 @@
       </c>
       <c r="C8" s="51" t="inlineStr">
         <is>
-          <t>Sun protection. R8. Chrono Beauty line. Competes with Shiseido Anessa.</t>
+          <t>Sun protection. Chrono Beauty line. Competes with Shiseido Anessa.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="16" customHeight="1">
       <c r="A9" s="50" t="inlineStr">
         <is>
-          <t>ADDED (Kao)</t>
+          <t>ADDED</t>
         </is>
       </c>
       <c r="B9" s="51" t="inlineStr">
@@ -3579,14 +3579,14 @@
       </c>
       <c r="C9" s="51" t="inlineStr">
         <is>
-          <t>Base makeup under Sofina. R8. Sweat-proof foundation.</t>
+          <t>Base makeup under Sofina. Sweat-proof foundation.</t>
         </is>
       </c>
     </row>
     <row r="10" ht="16" customHeight="1">
       <c r="A10" s="50" t="inlineStr">
         <is>
-          <t>ADDED (Kao)</t>
+          <t>ADDED</t>
         </is>
       </c>
       <c r="B10" s="51" t="inlineStr">
@@ -3603,7 +3603,7 @@
     <row r="11" ht="16" customHeight="1">
       <c r="A11" s="50" t="inlineStr">
         <is>
-          <t>ADDED (Kao)</t>
+          <t>ADDED</t>
         </is>
       </c>
       <c r="B11" s="51" t="inlineStr">
@@ -3613,14 +3613,14 @@
       </c>
       <c r="C11" s="51" t="inlineStr">
         <is>
-          <t>Kanebo skincare. R8. Lower priority.</t>
+          <t>Kanebo skincare. Lower priority.</t>
         </is>
       </c>
     </row>
     <row r="12" ht="16" customHeight="1">
       <c r="A12" s="50" t="inlineStr">
         <is>
-          <t>ADDED (Kao)</t>
+          <t>ADDED</t>
         </is>
       </c>
       <c r="B12" s="51" t="inlineStr">
@@ -3630,14 +3630,14 @@
       </c>
       <c r="C12" s="51" t="inlineStr">
         <is>
-          <t>Anti-aging. R8. Lower priority.</t>
+          <t>Anti-aging. Lower priority.</t>
         </is>
       </c>
     </row>
     <row r="13" ht="16" customHeight="1">
       <c r="A13" s="50" t="inlineStr">
         <is>
-          <t>UPDATED (Kao)</t>
+          <t>UPDATED</t>
         </is>
       </c>
       <c r="B13" s="51" t="inlineStr">
@@ -3654,7 +3654,7 @@
     <row r="14" ht="16" customHeight="1">
       <c r="A14" s="50" t="inlineStr">
         <is>
-          <t>ADDED (company)</t>
+          <t>ADDED</t>
         </is>
       </c>
       <c r="B14" s="51" t="inlineStr">
@@ -3671,7 +3671,7 @@
     <row r="15" ht="16" customHeight="1">
       <c r="A15" s="50" t="inlineStr">
         <is>
-          <t>ADDED (company)</t>
+          <t>ADDED</t>
         </is>
       </c>
       <c r="B15" s="51" t="inlineStr">
@@ -3688,7 +3688,7 @@
     <row r="16" ht="16" customHeight="1">
       <c r="A16" s="50" t="inlineStr">
         <is>
-          <t>ADDED (Shiseido)</t>
+          <t>ADDED</t>
         </is>
       </c>
       <c r="B16" s="51" t="inlineStr">
@@ -3705,7 +3705,7 @@
     <row r="17" ht="16" customHeight="1">
       <c r="A17" s="50" t="inlineStr">
         <is>
-          <t>ADDED (Shiseido)</t>
+          <t>ADDED</t>
         </is>
       </c>
       <c r="B17" s="51" t="inlineStr">
@@ -3722,7 +3722,7 @@
     <row r="18" ht="16" customHeight="1">
       <c r="A18" s="50" t="inlineStr">
         <is>
-          <t>ADDED (Shiseido)</t>
+          <t>ADDED</t>
         </is>
       </c>
       <c r="B18" s="51" t="inlineStr">
@@ -3739,7 +3739,7 @@
     <row r="19" ht="16" customHeight="1">
       <c r="A19" s="50" t="inlineStr">
         <is>
-          <t>ADDED (JP indie)</t>
+          <t>ADDED</t>
         </is>
       </c>
       <c r="B19" s="51" t="inlineStr">
